--- a/env/TestData.xlsx
+++ b/env/TestData.xlsx
@@ -1,109 +1,78 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kingu\Downloads\env2\env\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{488BFB3D-CDCC-4116-80E1-09C4E64A9132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-25965" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{39422533-2D24-42F0-AC72-C85E4D286E2E}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-25965" yWindow="4185" windowWidth="21600" windowHeight="11295" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
-  <si>
-    <t>Alice Green</t>
-  </si>
-  <si>
-    <t>Bob Smith</t>
-  </si>
-  <si>
-    <t>P001</t>
-  </si>
-  <si>
-    <t>P002</t>
-  </si>
-  <si>
-    <t>patient</t>
-  </si>
-  <si>
-    <t>patientID</t>
-  </si>
-  <si>
-    <t>date</t>
-  </si>
-  <si>
-    <t>duration</t>
-  </si>
-  <si>
-    <t>userID</t>
-  </si>
-  <si>
-    <t>U001</t>
-  </si>
-  <si>
-    <t>U002</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00196082"/>
+        <bgColor rgb="00196082"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF3F8"/>
+        <bgColor rgb="00EAF3F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -111,48 +80,151 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+  <cellXfs count="19">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -472,102 +544,717 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AB52E27-8A88-40E2-B451-F2D3B2A5267A}">
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="4">
-        <v>46093.375</v>
-      </c>
-      <c r="D2" s="8">
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>patientID</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>patient</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>duration</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>userID</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>Alice Green</t>
+        </is>
+      </c>
+      <c r="C2" s="14" t="n">
+        <v>46056.375</v>
+      </c>
+      <c r="D2" s="15" t="n">
         <v>45</v>
       </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="4">
-        <v>46092.5</v>
-      </c>
-      <c r="D3" s="8">
+      <c r="E2" s="12" t="inlineStr">
+        <is>
+          <t>U001</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>David Brown</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="n">
+        <v>46056.45833333334</v>
+      </c>
+      <c r="D3" s="18" t="n">
         <v>60</v>
       </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="8"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="8"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="8"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C7" s="5"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C9" s="5"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C10" s="5"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C11" s="5"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C12" s="5"/>
+      <c r="E3" s="16" t="inlineStr">
+        <is>
+          <t>U002</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>P007</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>Grace Taylor</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="n">
+        <v>46063.60416666666</v>
+      </c>
+      <c r="D4" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>U001</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>P002</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>Bob Smith</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="n">
+        <v>46070.375</v>
+      </c>
+      <c r="D5" s="18" t="n">
+        <v>60</v>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>U002</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Emma Wilson</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="n">
+        <v>46070.45833333334</v>
+      </c>
+      <c r="D6" s="15" t="n">
+        <v>45</v>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>U001</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>P008</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>Hannah Lewis</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="n">
+        <v>46070.58333333334</v>
+      </c>
+      <c r="D7" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>U002</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>P003</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Carol White</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>46077.39583333334</v>
+      </c>
+      <c r="D8" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>U001</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>P006</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>Frank Moore</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="n">
+        <v>46085.4375</v>
+      </c>
+      <c r="D9" s="16" t="n">
+        <v>120</v>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>U002</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>P010</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Julia Thompson</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="n">
+        <v>46086.59791666667</v>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>U001</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>P002</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>Bob Smith</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="n">
+        <v>46087.58333333334</v>
+      </c>
+      <c r="D11" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="E11" s="16" t="inlineStr">
+        <is>
+          <t>U002</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>P009</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>Ivan Martin</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="n">
+        <v>46090.35416666666</v>
+      </c>
+      <c r="D12" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>U001</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>David Brown</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="n">
+        <v>46092.375</v>
+      </c>
+      <c r="D13" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="E13" s="16" t="inlineStr">
+        <is>
+          <t>U002</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>P007</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Grace Taylor</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="n">
+        <v>46092.58333333334</v>
+      </c>
+      <c r="D14" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>U001</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>Alice Green</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="n">
+        <v>46097.41666666666</v>
+      </c>
+      <c r="D15" s="16" t="n">
+        <v>90</v>
+      </c>
+      <c r="E15" s="16" t="inlineStr">
+        <is>
+          <t>U002</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>Emma Wilson</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="n">
+        <v>46099.375</v>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>U001</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>P003</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>Carol White</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="n">
+        <v>46099.58333333334</v>
+      </c>
+      <c r="D17" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="E17" s="16" t="inlineStr">
+        <is>
+          <t>U002</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>P008</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>Hannah Lewis</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="n">
+        <v>46104.375</v>
+      </c>
+      <c r="D18" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>U001</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>P006</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>Frank Moore</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="n">
+        <v>46106.375</v>
+      </c>
+      <c r="D19" s="16" t="n">
+        <v>45</v>
+      </c>
+      <c r="E19" s="16" t="inlineStr">
+        <is>
+          <t>U002</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>P010</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>Julia Thompson</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="n">
+        <v>46106.45833333334</v>
+      </c>
+      <c r="D20" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>U001</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>P002</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>Bob Smith</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="n">
+        <v>46106.58333333334</v>
+      </c>
+      <c r="D21" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="E21" s="16" t="inlineStr">
+        <is>
+          <t>U002</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>David Brown</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="n">
+        <v>46111.41666666666</v>
+      </c>
+      <c r="D22" s="12" t="n">
+        <v>90</v>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>U001</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>P009</t>
+        </is>
+      </c>
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>Ivan Martin</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="n">
+        <v>46113.375</v>
+      </c>
+      <c r="D23" s="16" t="n">
+        <v>45</v>
+      </c>
+      <c r="E23" s="16" t="inlineStr">
+        <is>
+          <t>U002</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>Alice Green</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="n">
+        <v>46113.45833333334</v>
+      </c>
+      <c r="D24" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>U001</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>P007</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>Grace Taylor</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="n">
+        <v>46119.58333333334</v>
+      </c>
+      <c r="D25" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="E25" s="16" t="inlineStr">
+        <is>
+          <t>U002</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>P003</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>Carol White</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="n">
+        <v>46126.375</v>
+      </c>
+      <c r="D26" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>U001</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>P008</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>Hannah Lewis</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="n">
+        <v>46126.54166666666</v>
+      </c>
+      <c r="D27" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="E27" s="16" t="inlineStr">
+        <is>
+          <t>U002</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>Emma Wilson</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="n">
+        <v>46132.39583333334</v>
+      </c>
+      <c r="D28" s="12" t="n">
+        <v>90</v>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>U001</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>P010</t>
+        </is>
+      </c>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>Julia Thompson</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="n">
+        <v>46134.54166666666</v>
+      </c>
+      <c r="D29" s="16" t="n">
+        <v>45</v>
+      </c>
+      <c r="E29" s="16" t="inlineStr">
+        <is>
+          <t>U002</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>P006</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>Frank Moore</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="n">
+        <v>46140.625</v>
+      </c>
+      <c r="D30" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t>U001</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/env/TestData.xlsx
+++ b/env/TestData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -32,11 +32,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="YYYY-MM-DD HH:MM"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -400,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E30"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -427,10 +426,10 @@
         <v>Alice Green</v>
       </c>
       <c r="C2" t="str">
-        <v>Thursday, March 12, 2026</v>
+        <v>2026-02-03 09:00</v>
       </c>
       <c r="D2" t="str">
-        <v>45.00</v>
+        <v>45</v>
       </c>
       <c r="E2" t="str">
         <v>U001</v>
@@ -438,67 +437,220 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
+        <v>P004</v>
+      </c>
+      <c r="B3" t="str">
+        <v>David Brown</v>
+      </c>
+      <c r="C3" t="str">
+        <v>2026-02-03 11:00</v>
+      </c>
+      <c r="D3" t="str">
+        <v>60</v>
+      </c>
+      <c r="E3" t="str">
+        <v>U002</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>P007</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Grace Taylor</v>
+      </c>
+      <c r="C4" t="str">
+        <v>2026-02-10 14:30</v>
+      </c>
+      <c r="D4" t="str">
+        <v>30</v>
+      </c>
+      <c r="E4" t="str">
+        <v>U001</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
         <v>P002</v>
       </c>
-      <c r="B3" t="str">
+      <c r="B5" t="str">
         <v>Bob Smith</v>
       </c>
-      <c r="C3" t="str">
-        <v>Wednesday, March 11, 2026</v>
-      </c>
-      <c r="D3" t="str">
-        <v>60.00</v>
-      </c>
-      <c r="E3" t="str">
-        <v>U002</v>
+      <c r="C5" t="str">
+        <v>2026-02-17 09:00</v>
+      </c>
+      <c r="D5" t="str">
+        <v>60</v>
+      </c>
+      <c r="E5" t="str">
+        <v>U002</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>P005</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Emma Wilson</v>
+      </c>
+      <c r="C6" t="str">
+        <v>2026-02-17 11:00</v>
+      </c>
+      <c r="D6" t="str">
+        <v>45</v>
+      </c>
+      <c r="E6" t="str">
+        <v>U001</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>P008</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Hannah Lewis</v>
+      </c>
+      <c r="C7" t="str">
+        <v>2026-02-17 14:00</v>
+      </c>
+      <c r="D7" t="str">
+        <v>30</v>
+      </c>
+      <c r="E7" t="str">
+        <v>U002</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>P003</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Carol White</v>
+      </c>
+      <c r="C8" t="str">
+        <v>2026-02-24 09:30</v>
+      </c>
+      <c r="D8" t="str">
+        <v>60</v>
+      </c>
+      <c r="E8" t="str">
+        <v>U001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>P006</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Frank Moore</v>
+      </c>
+      <c r="C9" t="str">
+        <v>2026-03-04 10:30</v>
+      </c>
+      <c r="D9" t="str">
+        <v>120</v>
+      </c>
+      <c r="E9" t="str">
+        <v>U002</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>P010</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Julia Thompson</v>
+      </c>
+      <c r="C10" t="str">
+        <v>2026-03-05 14:21</v>
+      </c>
+      <c r="D10" t="str">
+        <v>60</v>
+      </c>
+      <c r="E10" t="str">
+        <v>U001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>P002</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Bob Smith</v>
+      </c>
+      <c r="C11" t="str">
+        <v>2026-03-06 14:00</v>
+      </c>
+      <c r="D11" t="str">
+        <v>60</v>
+      </c>
+      <c r="E11" t="str">
+        <v>U002</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>P009</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Ivan Martin</v>
+      </c>
+      <c r="C12" t="str">
+        <v>2026-03-09 08:30</v>
+      </c>
+      <c r="D12" t="str">
+        <v>45</v>
+      </c>
+      <c r="E12" t="str">
+        <v>U001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>P003</v>
+        <v>P004</v>
       </c>
       <c r="B13" t="str">
-        <v>Alice Green</v>
+        <v>David Brown</v>
       </c>
       <c r="C13" t="str">
-        <v>2026-02-03 09:00</v>
+        <v>2026-03-11 09:00</v>
       </c>
       <c r="D13" t="str">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="E13" t="str">
-        <v>U001</v>
+        <v>U002</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>P004</v>
+        <v>P007</v>
       </c>
       <c r="B14" t="str">
-        <v>James Carter</v>
+        <v>Grace Taylor</v>
       </c>
       <c r="C14" t="str">
-        <v>2026-02-03 11:00</v>
+        <v>2026-03-11 14:00</v>
       </c>
       <c r="D14" t="str">
         <v>60</v>
       </c>
       <c r="E14" t="str">
-        <v>U003</v>
+        <v>U001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>P005</v>
+        <v>P001</v>
       </c>
       <c r="B15" t="str">
-        <v>Carol White</v>
+        <v>Alice Green</v>
       </c>
       <c r="C15" t="str">
-        <v>2026-02-10 14:30</v>
+        <v>2026-03-16 10:00</v>
       </c>
       <c r="D15" t="str">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="E15" t="str">
         <v>U002</v>
@@ -506,16 +658,16 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>P006</v>
+        <v>P005</v>
       </c>
       <c r="B16" t="str">
-        <v>David Brown</v>
+        <v>Emma Wilson</v>
       </c>
       <c r="C16" t="str">
-        <v>2026-02-17 09:00</v>
+        <v>2026-03-18 09:00</v>
       </c>
       <c r="D16" t="str">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E16" t="str">
         <v>U001</v>
@@ -523,19 +675,19 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>P007</v>
+        <v>P003</v>
       </c>
       <c r="B17" t="str">
-        <v>Emma Wilson</v>
+        <v>Carol White</v>
       </c>
       <c r="C17" t="str">
-        <v>2026-02-17 11:00</v>
+        <v>2026-03-18 14:00</v>
       </c>
       <c r="D17" t="str">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="E17" t="str">
-        <v>U004</v>
+        <v>U002</v>
       </c>
     </row>
     <row r="18">
@@ -543,33 +695,33 @@
         <v>P008</v>
       </c>
       <c r="B18" t="str">
-        <v>Frank Moore</v>
+        <v>Hannah Lewis</v>
       </c>
       <c r="C18" t="str">
-        <v>2026-02-17 14:00</v>
+        <v>2026-03-23 09:00</v>
       </c>
       <c r="D18" t="str">
         <v>30</v>
       </c>
       <c r="E18" t="str">
-        <v>U002</v>
+        <v>U001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>P009</v>
+        <v>P006</v>
       </c>
       <c r="B19" t="str">
-        <v>Grace Taylor</v>
+        <v>Frank Moore</v>
       </c>
       <c r="C19" t="str">
-        <v>2026-02-24 09:30</v>
+        <v>2026-03-25 09:00</v>
       </c>
       <c r="D19" t="str">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E19" t="str">
-        <v>U003</v>
+        <v>U002</v>
       </c>
     </row>
     <row r="20">
@@ -577,13 +729,13 @@
         <v>P010</v>
       </c>
       <c r="B20" t="str">
-        <v>Steve Adams</v>
+        <v>Julia Thompson</v>
       </c>
       <c r="C20" t="str">
-        <v>2026-03-04 10:30</v>
+        <v>2026-03-25 11:00</v>
       </c>
       <c r="D20" t="str">
-        <v>120</v>
+        <v>45</v>
       </c>
       <c r="E20" t="str">
         <v>U001</v>
@@ -591,13 +743,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>P011</v>
+        <v>P002</v>
       </c>
       <c r="B21" t="str">
-        <v>Barry Jones</v>
+        <v>Bob Smith</v>
       </c>
       <c r="C21" t="str">
-        <v>2026-03-05 14:21</v>
+        <v>2026-03-25 14:00</v>
       </c>
       <c r="D21" t="str">
         <v>60</v>
@@ -608,64 +760,64 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>P012</v>
+        <v>P004</v>
       </c>
       <c r="B22" t="str">
-        <v>Bob Harris</v>
+        <v>David Brown</v>
       </c>
       <c r="C22" t="str">
-        <v>2026-03-06 14:00</v>
+        <v>2026-03-30 10:00</v>
       </c>
       <c r="D22" t="str">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="E22" t="str">
-        <v>U004</v>
+        <v>U001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>P013</v>
+        <v>P009</v>
       </c>
       <c r="B23" t="str">
-        <v>Hannah Lewis</v>
+        <v>Ivan Martin</v>
       </c>
       <c r="C23" t="str">
-        <v>2026-03-09 08:30</v>
+        <v>2026-04-01 09:00</v>
       </c>
       <c r="D23" t="str">
         <v>45</v>
       </c>
       <c r="E23" t="str">
-        <v>U001</v>
+        <v>U002</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>P014</v>
+        <v>P001</v>
       </c>
       <c r="B24" t="str">
-        <v>Ivan Martin</v>
+        <v>Alice Green</v>
       </c>
       <c r="C24" t="str">
-        <v>2026-03-11 09:00</v>
+        <v>2026-04-01 11:00</v>
       </c>
       <c r="D24" t="str">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E24" t="str">
-        <v>U003</v>
+        <v>U001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>P015</v>
+        <v>P007</v>
       </c>
       <c r="B25" t="str">
-        <v>Julia Thompson</v>
+        <v>Grace Taylor</v>
       </c>
       <c r="C25" t="str">
-        <v>2026-03-11 14:00</v>
+        <v>2026-04-07 14:00</v>
       </c>
       <c r="D25" t="str">
         <v>60</v>
@@ -676,16 +828,16 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>P016</v>
+        <v>P003</v>
       </c>
       <c r="B26" t="str">
-        <v>Kevin Garcia</v>
+        <v>Carol White</v>
       </c>
       <c r="C26" t="str">
-        <v>2026-03-16 10:00</v>
+        <v>2026-04-14 09:00</v>
       </c>
       <c r="D26" t="str">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="E26" t="str">
         <v>U001</v>
@@ -693,50 +845,50 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>P017</v>
+        <v>P008</v>
       </c>
       <c r="B27" t="str">
-        <v>Laura Martinez</v>
+        <v>Hannah Lewis</v>
       </c>
       <c r="C27" t="str">
-        <v>2026-03-18 09:00</v>
+        <v>2026-04-14 13:00</v>
       </c>
       <c r="D27" t="str">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="E27" t="str">
-        <v>U004</v>
+        <v>U002</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>P018</v>
+        <v>P005</v>
       </c>
       <c r="B28" t="str">
-        <v>Marcus Robinson</v>
+        <v>Emma Wilson</v>
       </c>
       <c r="C28" t="str">
-        <v>2026-03-18 14:00</v>
+        <v>2026-04-20 09:30</v>
       </c>
       <c r="D28" t="str">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="E28" t="str">
-        <v>U003</v>
+        <v>U001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>P019</v>
+        <v>P010</v>
       </c>
       <c r="B29" t="str">
-        <v>Nina Clark</v>
+        <v>Julia Thompson</v>
       </c>
       <c r="C29" t="str">
-        <v>2026-03-23 09:00</v>
+        <v>2026-04-22 13:00</v>
       </c>
       <c r="D29" t="str">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E29" t="str">
         <v>U002</v>
@@ -744,211 +896,24 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>P020</v>
+        <v>P006</v>
       </c>
       <c r="B30" t="str">
-        <v>Oliver Rodriguez</v>
+        <v>Frank Moore</v>
       </c>
       <c r="C30" t="str">
-        <v>2026-03-25 09:00</v>
+        <v>2026-04-28 15:00</v>
       </c>
       <c r="D30" t="str">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="E30" t="str">
-        <v>U001</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v>P021</v>
-      </c>
-      <c r="B31" t="str">
-        <v>Paula Lewis</v>
-      </c>
-      <c r="C31" t="str">
-        <v>2026-03-25 11:00</v>
-      </c>
-      <c r="D31" t="str">
-        <v>45</v>
-      </c>
-      <c r="E31" t="str">
-        <v>U004</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <v>P022</v>
-      </c>
-      <c r="B32" t="str">
-        <v>Quinn Walker</v>
-      </c>
-      <c r="C32" t="str">
-        <v>2026-03-25 14:00</v>
-      </c>
-      <c r="D32" t="str">
-        <v>60</v>
-      </c>
-      <c r="E32" t="str">
-        <v>U002</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="str">
-        <v>P023</v>
-      </c>
-      <c r="B33" t="str">
-        <v>Rachel Hall</v>
-      </c>
-      <c r="C33" t="str">
-        <v>2026-03-30 10:00</v>
-      </c>
-      <c r="D33" t="str">
-        <v>90</v>
-      </c>
-      <c r="E33" t="str">
-        <v>U003</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v>P024</v>
-      </c>
-      <c r="B34" t="str">
-        <v>Sam Allen</v>
-      </c>
-      <c r="C34" t="str">
-        <v>2026-04-01 09:00</v>
-      </c>
-      <c r="D34" t="str">
-        <v>45</v>
-      </c>
-      <c r="E34" t="str">
-        <v>U001</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="str">
-        <v>P025</v>
-      </c>
-      <c r="B35" t="str">
-        <v>Tina Young</v>
-      </c>
-      <c r="C35" t="str">
-        <v>2026-04-01 11:00</v>
-      </c>
-      <c r="D35" t="str">
-        <v>45</v>
-      </c>
-      <c r="E35" t="str">
-        <v>U002</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="str">
-        <v>P026</v>
-      </c>
-      <c r="B36" t="str">
-        <v>Uma Hernandez</v>
-      </c>
-      <c r="C36" t="str">
-        <v>2026-04-07 14:00</v>
-      </c>
-      <c r="D36" t="str">
-        <v>60</v>
-      </c>
-      <c r="E36" t="str">
-        <v>U004</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="str">
-        <v>P027</v>
-      </c>
-      <c r="B37" t="str">
-        <v>Victor King</v>
-      </c>
-      <c r="C37" t="str">
-        <v>2026-04-14 09:00</v>
-      </c>
-      <c r="D37" t="str">
-        <v>30</v>
-      </c>
-      <c r="E37" t="str">
-        <v>U001</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="str">
-        <v>P028</v>
-      </c>
-      <c r="B38" t="str">
-        <v>Wendy Wright</v>
-      </c>
-      <c r="C38" t="str">
-        <v>2026-04-14 13:00</v>
-      </c>
-      <c r="D38" t="str">
-        <v>60</v>
-      </c>
-      <c r="E38" t="str">
-        <v>U003</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="str">
-        <v>P029</v>
-      </c>
-      <c r="B39" t="str">
-        <v>Xander Scott</v>
-      </c>
-      <c r="C39" t="str">
-        <v>2026-04-20 09:30</v>
-      </c>
-      <c r="D39" t="str">
-        <v>90</v>
-      </c>
-      <c r="E39" t="str">
-        <v>U002</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="str">
-        <v>P030</v>
-      </c>
-      <c r="B40" t="str">
-        <v>Yasmin Green</v>
-      </c>
-      <c r="C40" t="str">
-        <v>2026-04-22 13:00</v>
-      </c>
-      <c r="D40" t="str">
-        <v>45</v>
-      </c>
-      <c r="E40" t="str">
-        <v>U004</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="str">
-        <v>P031</v>
-      </c>
-      <c r="B41" t="str">
-        <v>Zoe Baker</v>
-      </c>
-      <c r="C41" t="str">
-        <v>2026-04-28 15:00</v>
-      </c>
-      <c r="D41" t="str">
-        <v>60</v>
-      </c>
-      <c r="E41" t="str">
         <v>U001</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E30"/>
   </ignoredErrors>
 </worksheet>
 </file>